--- a/research/structural-profiles-pilot/worksheet/structural_profiles_reference_and_owner_review.xlsx
+++ b/research/structural-profiles-pilot/worksheet/structural_profiles_reference_and_owner_review.xlsx
@@ -18,13 +18,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA_DICTIONARY" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'S1_S5_RUBRIC'!$A$3:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'S1_S5_RUBRIC'!$A$3:$G$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'S1_S5_RUBRIC'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'STAGE_TAXONOMY'!$A$3:$H$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'STAGE_TAXONOMY'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SCOPED_PROFILES'!$A$3:$AF$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'SCOPED_PROFILES'!$1:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EXCEPTION_RULES'!$A$3:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EXCEPTION_RULES'!$A$3:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'EXCEPTION_RULES'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'OWNER_DECISIONS'!$A$3:$R$103</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'OWNER_DECISIONS'!$1:$3</definedName>
@@ -144,8 +144,9 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -255,6 +256,11 @@
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>Cell role: generated/reference.</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cell role: generated/reference.</t>
       </text>
@@ -1366,7 +1372,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>S1-S5, C1-C8, rationales, source IDs, dates, confidence, notes, lifecycle phases, country/governance rows, exception results, owner decisions, and all approval/canonicalization fields must remain blank in this package.</t>
+          <t>S1-S5, C1-C8, rationales, source IDs, dates, confidence, notes, country/governance rows, exception results, owner decisions, and all approval/canonicalization fields must remain blank in this package.</t>
         </is>
       </c>
     </row>
@@ -1404,21 +1410,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Reference only. Higher is always structurally easier. Keep all five dimensions separate; never sum, average, weight, rank, or percentage-transform them.</t>
+          <t>Reference only. Higher is always structurally easier. Keep all five dimensions separate; never sum, average, weight, rank, or percentage-transform them. The 2 anchor is operational guidance, not a cardinal midpoint or new method rule.</t>
         </is>
       </c>
     </row>
@@ -1441,15 +1448,20 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>0_means</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>2_guidance</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>4_means</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>0_means</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>coding_instruction</t>
         </is>
@@ -1473,17 +1485,22 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>Progress occurs primarily through physical transformation, biological processes, construction, or accumulated operating time.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Stage progress materially combines informational and physical, biological, or operational work; neither clearly dominates under the stated scope.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
           <t>Progress occurs primarily through information processing, analysis, design, inference, communication, or software.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Progress occurs primarily through physical transformation, biological processes, construction, or accumulated operating time.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Code how progress occurs within this stage, not its share of a wider schedule. Critical-path role is separate.</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Code how progress occurs within this stage, not its share of a wider schedule. Critical-path role is separate. Values 1 and 3 require an explicit intermediate-judgment rationale; do not interpolate mechanically.</t>
         </is>
       </c>
     </row>
@@ -1505,17 +1522,22 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>Cycles take years to decades.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>The ordinary learn-test-revise cycle is generally measured in weeks to months, rather than minutes/days or years/decades.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
           <t>Learn-test-revise cycles occur in minutes to days.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Cycles take years to decades.</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Classify the ordinary scoped feedback loop, not an ideal demo.</t>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Classify the ordinary scoped feedback loop, not an ideal demo. Values 1 and 3 require an explicit intermediate-judgment rationale; do not interpolate mechanically.</t>
         </is>
       </c>
     </row>
@@ -1537,17 +1559,22 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
+          <t>Attempts are scarce and expensive.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Attempts require meaningful resources or scarce systems but remain repeatable; throughput or parallelism is material but constrained.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>Attempts are near-free and parallel.</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Attempts are scarce and expensive.</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>The rationale must address both marginal cost per attempt and attainable parallel or serial throughput. Preserve divergence and lower confidence.</t>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>The rationale must address both marginal cost per attempt and attainable parallel or serial throughput. Preserve divergence and lower confidence. Values 1 and 3 require an explicit intermediate-judgment rationale; do not interpolate mechanically.</t>
         </is>
       </c>
     </row>
@@ -1569,17 +1596,22 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
+          <t>Clock time is dominated by physical floors.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Physical processes create meaningful delay, but no single physical, biological, construction, curing, healing, or qualification floor dominates the entire scoped stage.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
           <t>No construction, growth, curing, healing, or qualification floor dominates elapsed time.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Clock time is dominated by physical floors.</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Code intrinsic physical time floors at the scoped stage.</t>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Code intrinsic physical time floors at the scoped stage. Values 1 and 3 require an explicit intermediate-judgment rationale; do not interpolate mechanically.</t>
         </is>
       </c>
     </row>
@@ -1601,24 +1633,30 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
+          <t>Errors are catastrophic or irreversible.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Errors create material cost, delay, or review burdens, but are usually containable and reversible within the stated scope.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
           <t>Errors are cheap, reversible, and low-externality.</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Errors are catastrophic or irreversible.</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Classify consequences and reversibility within scope.</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Classify consequences and reversibility within scope. Values 1 and 3 require an explicit intermediate-judgment rationale; do not interpolate mechanically.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F8"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
+  <autoFilter ref="A3:G8"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1639,7 +1677,7 @@
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -1716,7 +1754,11 @@
           <t>Requirements and architecture</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Includes requirements definition, interface specification, architecture, and system trade-offs for features in an established production codebase. Excludes implementation, verification, deployment, and post-deployment operations.</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1754,7 +1796,11 @@
           <t>Implementation</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Includes coding, configuration, refactoring, and integration work that implements an approved change in an established production codebase. Excludes requirements and architecture, formal verification, production deployment, and ongoing operations.</t>
+        </is>
+      </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>2</t>
@@ -1792,7 +1838,11 @@
           <t>Verification and validation</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Includes reviews, testing, defect reproduction, and validation of a software change before production release. Excludes feature implementation, production rollout, and post-deployment operations.</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1830,7 +1880,11 @@
           <t>Deployment</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Includes packaging, release preparation, rollout, migration, and production enablement for a mature software change. Excludes feature development and ongoing production operations after the rollout is complete.</t>
+        </is>
+      </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
           <t>4</t>
@@ -1868,7 +1922,11 @@
           <t>Operations and maintenance</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Includes monitoring, incident response, bug fixing, routine upkeep, and small corrective changes after deployment in an established production system. Excludes initial feature design and the release rollout itself.</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <t>5</t>
@@ -1906,7 +1964,11 @@
           <t>Product design</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Includes product requirements, engineering design, component definition, and design trade-offs for new-product introduction. Excludes manufacturing-process design, tooling acquisition, line commissioning, and routine production.</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1944,7 +2006,11 @@
           <t>Process engineering</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Includes defining the manufacturing sequence, process specifications, controls, and production methods for new-product introduction. Excludes product design, sourcing or building tooling, line commissioning, and routine production execution.</t>
+        </is>
+      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>2</t>
@@ -1982,7 +2048,11 @@
           <t>Supply and tooling</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Includes supplier and material readiness plus sourcing, design, procurement, and preparation of production tooling and equipment for the frozen manufacturing pathway. Excludes on-site line commissioning and routine production operations.</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>3</t>
@@ -2020,7 +2090,11 @@
           <t>Retooling and commissioning</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Includes installing, changing over, debugging, and commissioning production equipment and lines for product introduction and ramp. Excludes upstream product or process design and ongoing production after the line is released to operations.</t>
+        </is>
+      </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>4</t>
@@ -2058,7 +2132,11 @@
           <t>Production planning and scheduling</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Includes capacity, material, labor, sequencing, and production-schedule planning during ramp and operations. Excludes physical production execution and real-time process control.</t>
+        </is>
+      </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
           <t>5</t>
@@ -2096,7 +2174,11 @@
           <t>Production and process control</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Includes executing production and monitoring or adjusting process conditions during ramp and operations. Excludes upstream product design, line commissioning, and a separate regulated product-qualification pathway.</t>
+        </is>
+      </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
           <t>6</t>
@@ -2134,7 +2216,11 @@
           <t>Quality assurance</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Includes in-process, end-of-line, and ongoing production quality assurance during ramp and operations. It does not represent a separate regulated product-qualification pathway.</t>
+        </is>
+      </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
           <t>7</t>
@@ -2172,7 +2258,11 @@
           <t>Maintenance and continuous improvement</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Includes production-equipment upkeep, reliability work, yield improvement, and iterative process improvement during operations. Excludes initial line commissioning and new-product design.</t>
+        </is>
+      </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
           <t>8</t>
@@ -2210,7 +2300,11 @@
           <t>Concept and design</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for tokamak theory and system-design work directed toward a pilot-relevant concept. Excludes downstream experiment-loop, subsystem, build, demonstration, licensing, and grid-connection work.</t>
+        </is>
+      </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -2248,7 +2342,11 @@
           <t>Theory and system design</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Includes tokamak theory, system requirements, architecture, and pilot-plant design trade-offs under the frozen pathway. Excludes detailed subsystem engineering, component fabrication, construction, and commissioning.</t>
+        </is>
+      </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
           <t>2</t>
@@ -2286,7 +2384,11 @@
           <t>Digital experiment loop</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for simulation and experiment-selection work supporting tokamak research and pilot-relevant design. Excludes physical diagnostic operation, plasma-control execution, and plant build.</t>
+        </is>
+      </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
           <t>3</t>
@@ -2324,7 +2426,11 @@
           <t>Simulation</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Includes computational modelling and simulation of plasma, components, or integrated tokamak behaviour for research and experiment support. Excludes physical experiment execution, diagnostics operation, and component fabrication.</t>
+        </is>
+      </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
           <t>4</t>
@@ -2362,7 +2468,11 @@
           <t>Experiment selection</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Includes selecting, prioritising, and sequencing tokamak experiments against stated research or pilot-development objectives. Excludes executing experiments, collecting diagnostics, and operating plasma controls.</t>
+        </is>
+      </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
           <t>5</t>
@@ -2400,7 +2510,11 @@
           <t>Plasma operations</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for diagnostics and plasma-control work in pilot-relevant tokamak experiments. Excludes plant-subsystem engineering, component fabrication, and facility construction.</t>
+        </is>
+      </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
           <t>6</t>
@@ -2438,7 +2552,11 @@
           <t>Diagnostics</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Includes design, preparation, use, and interpretation of measurement systems for pilot-relevant tokamak experiments. Excludes plasma-control actuation and plant-subsystem fabrication or integration.</t>
+        </is>
+      </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
           <t>7</t>
@@ -2476,7 +2594,11 @@
           <t>Plasma control</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Includes development, testing, and operation of control methods and systems used to shape, sustain, or terminate plasma in the frozen tokamak pathway. Excludes diagnostic measurement and broader plant-subsystem construction.</t>
+        </is>
+      </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
           <t>8</t>
@@ -2514,7 +2636,11 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for pilot-relevant materials discovery, screening, and qualification under the tokamak pathway. Excludes subsystem design, component fabrication, and facility construction.</t>
+        </is>
+      </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
           <t>9</t>
@@ -2552,7 +2678,11 @@
           <t>Materials discovery and screening</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Includes identifying and screening candidate materials for pilot-relevant tokamak conditions. Excludes formal qualification, component fabrication, and production-scale supply.</t>
+        </is>
+      </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
           <t>10</t>
@@ -2590,7 +2720,11 @@
           <t>Materials qualification</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Includes testing and qualifying candidate materials against pilot-relevant loads, environments, and requirements. Excludes initial discovery and screening, component fabrication, and commercial-fleet qualification.</t>
+        </is>
+      </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
           <t>11</t>
@@ -2628,7 +2762,11 @@
           <t>Plant subsystems</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for pilot-relevant design, engineering, testing, and pre-integration of magnets, heating and current drive, plasma-facing components, tritium and fuel cycle, and blankets under the tokamak pathway. Excludes component fabrication after design maturity, site construction, and integrated commissioning.</t>
+        </is>
+      </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
           <t>12</t>
@@ -2666,7 +2804,11 @@
           <t>Magnets</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Includes pilot-relevant magnet design, engineering, testing, and pre-integration under the tokamak pathway. Excludes fabrication after design maturity, site construction, integrated commissioning, and commercial-fleet rollout.</t>
+        </is>
+      </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
           <t>13</t>
@@ -2704,7 +2846,11 @@
           <t>Heating and current drive</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Includes pilot-relevant heating and current-drive design, engineering, testing, and pre-integration under the tokamak pathway. Excludes fabrication after design maturity, site construction, integrated commissioning, and commercial-fleet rollout.</t>
+        </is>
+      </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
           <t>14</t>
@@ -2742,7 +2888,11 @@
           <t>Plasma-facing components</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Includes pilot-relevant plasma-facing component design, engineering, testing, and pre-integration under the tokamak pathway. Excludes fabrication after design maturity, site construction, integrated commissioning, and commercial-fleet rollout.</t>
+        </is>
+      </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
           <t>15</t>
@@ -2780,7 +2930,11 @@
           <t>Tritium and fuel cycle</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Includes pilot-relevant tritium and fuel-cycle design, engineering, testing, and pre-integration under the tokamak pathway. Excludes fabrication after design maturity, site construction, integrated commissioning, and commercial-fleet rollout.</t>
+        </is>
+      </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
           <t>16</t>
@@ -2818,7 +2972,11 @@
           <t>Blankets</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Includes pilot-relevant blanket design, engineering, testing, and pre-integration under the tokamak pathway. Excludes fabrication after design maturity, site construction, integrated commissioning, and commercial-fleet rollout.</t>
+        </is>
+      </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
           <t>17</t>
@@ -2856,7 +3014,11 @@
           <t>Build</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for pilot-relevant component fabrication after design maturity and construction of the tokamak pilot facility. Excludes earlier design and qualification work plus later commissioning and demonstration.</t>
+        </is>
+      </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
           <t>18</t>
@@ -2894,7 +3056,11 @@
           <t>Component fabrication</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Includes pilot-relevant fabrication after design maturity under the tokamak pathway. Excludes earlier subsystem design or materials qualification, site construction, integrated commissioning, and commercial-fleet production.</t>
+        </is>
+      </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
           <t>19</t>
@@ -2932,7 +3098,11 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Includes site work, assembly, installation, and construction of the pilot-relevant tokamak facility. Excludes off-site component fabrication, earlier subsystem design, commissioning, and commercial-fleet rollout.</t>
+        </is>
+      </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
           <t>20</t>
@@ -2970,7 +3140,11 @@
           <t>Demonstration and assurance</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for commissioning and reliability demonstration of the assembled pilot-relevant tokamak system. Excludes facility construction and routine commercial operations.</t>
+        </is>
+      </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
           <t>21</t>
@@ -3008,7 +3182,11 @@
           <t>Commissioning</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Includes bringing the assembled pilot-relevant tokamak facility into test operation, checking interfaces, and establishing integrated readiness. Excludes construction and the subsequent reliability-demonstration campaign.</t>
+        </is>
+      </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
           <t>22</t>
@@ -3046,7 +3224,11 @@
           <t>Reliability demonstration</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Includes sustained or repeated integrated testing used to demonstrate pilot-relevant reliability and operating performance. Excludes initial commissioning and routine commercial-fleet operations.</t>
+        </is>
+      </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
           <t>23</t>
@@ -3084,7 +3266,11 @@
           <t>Approval and connection</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Parent scope for pilot-facility licensing plus connection and technical integration for pilot demonstration. Excludes commercial-fleet licensing and rollout.</t>
+        </is>
+      </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
           <t>24</t>
@@ -3122,7 +3308,11 @@
           <t>Licensing</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Includes licensing and regulatory approval work for the pilot-relevant tokamak facility and demonstration under the frozen pathway. Excludes grid connection and commercial-fleet licensing.</t>
+        </is>
+      </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
           <t>25</t>
@@ -3160,7 +3350,11 @@
           <t>Grid integration</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Includes connection and technical integration for pilot demonstration under the tokamak pathway. Excludes commercial fleet rollout and broader market diffusion.</t>
+        </is>
+      </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
           <t>26</t>
@@ -3178,6 +3372,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <autoFilter ref="A3:H42"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -3209,7 +3404,7 @@
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -3442,7 +3637,11 @@
           <t>Mature production-software feature development, debugging, testing, integration, deployment, operations, and maintenance in an established codebase</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3508,7 +3707,11 @@
           <t>Mature production-software feature development, debugging, testing, integration, deployment, operations, and maintenance in an established codebase</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3574,7 +3777,11 @@
           <t>Mature production-software feature development, debugging, testing, integration, deployment, operations, and maintenance in an established codebase</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3640,7 +3847,11 @@
           <t>Mature production-software feature development, debugging, testing, integration, deployment, operations, and maintenance in an established codebase</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>commercial_deployment</t>
+        </is>
+      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3706,7 +3917,11 @@
           <t>Mature production-software feature development, debugging, testing, integration, deployment, operations, and maintenance in an established codebase</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3772,7 +3987,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3838,7 +4057,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3904,7 +4127,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>scale_up</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -3970,7 +4197,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>scale_up</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4036,7 +4267,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4102,7 +4337,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4168,7 +4407,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4234,7 +4477,11 @@
           <t>New-product introduction and operations in medium-to-high-volume discrete manufacturing, from product and process engineering through tooling, commissioning, quality, production, maintenance, and iterative improvement</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4300,7 +4547,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4366,7 +4617,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4432,7 +4687,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4498,7 +4757,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4564,7 +4827,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4630,7 +4897,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4696,7 +4967,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>qualification</t>
+        </is>
+      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4762,7 +5037,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4828,7 +5107,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4894,7 +5177,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -4960,7 +5247,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5026,7 +5317,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5092,7 +5387,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>scale_up</t>
+        </is>
+      </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5158,7 +5457,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>demonstration</t>
+        </is>
+      </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5224,7 +5527,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>demonstration</t>
+        </is>
+      </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5290,7 +5597,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>demonstration</t>
+        </is>
+      </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5356,7 +5667,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>qualification</t>
+        </is>
+      </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5422,7 +5737,11 @@
           <t>Tokamak research through component and subsystem development, materials qualification, facility build, commissioning, integrated demonstration, and pilot-plant readiness</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>demonstration</t>
+        </is>
+      </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>not_assessed</t>
@@ -5453,6 +5772,7 @@
       <c r="AF34" s="6" t="inlineStr"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <autoFilter ref="A3:AF34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AF1"/>
@@ -5509,7 +5829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5562,7 +5882,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Absolute Fable-versus-blind difference is 2 or more on an S-dimension.</t>
+          <t>Absolute Fable-versus-independent difference is 2 or more on an S-dimension.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -5685,19 +6005,19 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Defer missing evidence when necessary; never invent a source ID.</t>
+          <t>Route to needs_better_evidence when necessary; never invent a source ID.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>low_confidence_load_bearing_stage</t>
+          <t>missing_score</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>A load-bearing stage has low coding confidence.</t>
+          <t>Either submission is missing or has an invalid S value for the comparison.</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5707,24 +6027,24 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Route for evidence or domain review without manufacturing certainty.</t>
+          <t>Keep the audit row, mark missing_score, and never silently omit it.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>scope_pathway_application_or_lifecycle_ambiguity</t>
+          <t>low_confidence_load_bearing_stage</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>A scope, pathway, application, or lifecycle field is ambiguous.</t>
+          <t>A load-bearing stage has low coding confidence.</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5734,44 +6054,72 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Resolve scope before selecting a value; blank is allowed.</t>
+          <t>Route for evidence or domain review without manufacturing certainty.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>scope_pathway_application_or_lifecycle_ambiguity</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>A scope, pathway, application, or lifecycle field is ambiguous.</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Resolve scope before selecting a value; blank is allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>routine_fusion_domain_review</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Every frozen fusion profile, whether or not another flag fires.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>No, unless another exception applies</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Queue as routine domain review; keep it distinct from an owner decision.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E11"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
+  <autoFilter ref="A3:E12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -7911,13 +8259,14 @@
       <c r="R103" s="7" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <autoFilter ref="A3:R103"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="M4:M103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the canonical list or leave blank." promptTitle="Allowed values" prompt="Use a canonical allowed value. Blank remains allowed." type="list">
-      <formula1>"prefer_fable,prefer_blind,preserve_disagreement,needs_domain_review,defer_missing_evidence"</formula1>
+      <formula1>"prefer_fable,prefer_independent,preserve_disagreement,needs_domain_review,needs_better_evidence"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the canonical list or leave blank." promptTitle="Allowed values" prompt="Use a canonical allowed value. Blank remains allowed." type="list">
       <formula1>"S1,S2,S3,S4,S5"</formula1>
@@ -9787,6 +10136,7 @@
       <c r="AE53" s="7" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <autoFilter ref="A3:AE53"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AE1"/>
@@ -11675,6 +12025,7 @@
       <c r="AE53" s="7" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <autoFilter ref="A3:AE53"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AE1"/>
@@ -11881,7 +12232,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Description.</t>
+          <t>Frozen V1 statement of activity included and material exclusions.</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
@@ -11892,7 +12243,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>reference populated where supported</t>
         </is>
       </c>
     </row>
@@ -12193,7 +12544,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>One canonical lifecycle value; blank here where assignment needs judgment.</t>
+          <t>Owner-approved primary V1 coding context; it does not claim that the stage occurs exclusively in that lifecycle phase.</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -12208,7 +12559,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>reference populated where supported</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13359,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>reference populated where supported</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13387,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>reference populated where supported</t>
         </is>
       </c>
     </row>
@@ -13064,7 +13415,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>reference populated where supported</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13443,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>reference populated where supported</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15957,7 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>prefer_fable | prefer_blind | preserve_disagreement | needs_domain_review | defer_missing_evidence</t>
+          <t>prefer_fable | prefer_independent | preserve_disagreement | needs_domain_review | needs_better_evidence</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -15793,6 +16144,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <autoFilter ref="A3:F141"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/research/structural-profiles-pilot/worksheet/structural_profiles_reference_and_owner_review.xlsx
+++ b/research/structural-profiles-pilot/worksheet/structural_profiles_reference_and_owner_review.xlsx
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Fable later proposes the seed coding. A blind independent model codes without seeing that submission. Codex later validates and produces a dimension-specific exception report. Jinhua reviews exceptions only. Domain experts later review all fusion rows and other routed cases.</t>
+          <t>The completed seed coding was produced in Claude Code using Claude Opus 5. The independent coding was produced by Codex using GPT-5.6 at extra-high reasoning effort. Fable remains the framework architect, not the row-level coder. Jinhua reviews routed exceptions only; domain experts later review all fusion rows and other routed cases.</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Send only fable_submission_template.xlsx to Fable. Send only blind_submission_template.xlsx to the blind model. Keep this owner workbook and all returned submissions out of the blind task.</t>
+          <t>The original Fable-named template is a historical handoff artifact. For reconciliation, use the immutable seed_submission_v1.csv and independent_submission_v1.csv copies pinned to their recorded PR heads.</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Absolute Fable-versus-independent difference is 2 or more on an S-dimension.</t>
+          <t>Absolute seed-versus-independent difference is 2 or more on an S-dimension.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -6144,12 +6144,12 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
@@ -6199,32 +6199,32 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>fable_value</t>
+          <t>seed_value</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>blind_value</t>
+          <t>independent_value</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>fable_rationale</t>
+          <t>seed_rationale</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>blind_rationale</t>
+          <t>independent_rationale</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>fable_source_ids</t>
+          <t>seed_source_ids</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>blind_source_ids</t>
+          <t>independent_source_ids</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
@@ -8266,7 +8266,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="M4:M103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the canonical list or leave blank." promptTitle="Allowed values" prompt="Use a canonical allowed value. Blank remains allowed." type="list">
-      <formula1>"prefer_fable,prefer_independent,preserve_disagreement,needs_domain_review,needs_better_evidence"</formula1>
+      <formula1>"prefer_seed,prefer_independent,preserve_disagreement,needs_domain_review,needs_better_evidence"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the canonical list or leave blank." promptTitle="Allowed values" prompt="Use a canonical allowed value. Blank remains allowed." type="list">
       <formula1>"S1,S2,S3,S4,S5"</formula1>
@@ -15779,12 +15779,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>fable_value</t>
+          <t>seed_value</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Fable value.</t>
+          <t>Seed value.</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr"/>
@@ -15807,12 +15807,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>blind_value</t>
+          <t>independent_value</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Blind value.</t>
+          <t>Independent value.</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr"/>
@@ -15835,12 +15835,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>fable_rationale</t>
+          <t>seed_rationale</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Fable rationale.</t>
+          <t>Seed rationale.</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr"/>
@@ -15863,12 +15863,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>blind_rationale</t>
+          <t>independent_rationale</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Blind rationale.</t>
+          <t>Independent rationale.</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr"/>
@@ -15891,12 +15891,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>fable_source_ids</t>
+          <t>seed_source_ids</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Fable source ids.</t>
+          <t>Seed source ids.</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr"/>
@@ -15919,12 +15919,12 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>blind_source_ids</t>
+          <t>independent_source_ids</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Blind source ids.</t>
+          <t>Independent source ids.</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>prefer_fable | prefer_independent | preserve_disagreement | needs_domain_review | needs_better_evidence</t>
+          <t>prefer_seed | prefer_independent | preserve_disagreement | needs_domain_review | needs_better_evidence</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
